--- a/product_selector_out/STM32H5 series - diff.xlsx
+++ b/product_selector_out/STM32H5 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$255</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,11 +52,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
@@ -68,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E228"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5430</v>
+        <v>5421</v>
       </c>
     </row>
     <row r="18">
@@ -3071,22 +3071,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3098,18 +3098,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3121,25 +3125,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3154,10 +3162,10 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -3166,54 +3174,46 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3225,22 +3225,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3252,22 +3252,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3306,22 +3306,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -3333,18 +3333,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3356,70 +3360,74 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -3428,25 +3436,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -3455,25 +3463,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -3482,54 +3490,46 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3541,22 +3541,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3568,18 +3568,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3591,25 +3595,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3624,10 +3632,10 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -3636,7 +3644,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3654,7 +3662,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E145" s="5" t="inlineStr">
+      <c r="E145" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -3663,7 +3671,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3681,7 +3689,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -3690,7 +3698,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3708,7 +3716,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E147" s="7" t="inlineStr">
+      <c r="E147" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -3717,7 +3725,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3735,7 +3743,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E148" s="5" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -3744,7 +3752,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3762,7 +3770,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -3771,7 +3779,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3789,7 +3797,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E150" s="7" t="inlineStr">
+      <c r="E150" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -3798,7 +3806,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3821,7 +3829,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3844,107 +3852,115 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3959,19 +3975,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3981,51 +3997,51 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E159" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4040,19 +4056,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4062,58 +4078,62 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -4125,18 +4145,18 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -4148,18 +4168,18 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -4171,18 +4191,18 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -4194,76 +4214,88 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4278,10 +4310,10 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -4290,7 +4322,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4305,10 +4337,10 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -4317,7 +4349,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4332,10 +4364,10 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -4344,7 +4376,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4359,10 +4391,10 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E173" s="7" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -4371,7 +4403,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4386,19 +4418,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4413,10 +4445,10 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -4425,7 +4457,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4440,10 +4472,10 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -4452,7 +4484,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4475,7 +4507,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4498,242 +4530,226 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E180" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E181" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E183" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E184" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E185" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D186" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E186" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4748,10 +4764,10 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr">
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -4760,7 +4776,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4778,7 +4794,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -4787,7 +4803,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4805,7 +4821,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -4814,7 +4830,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4832,7 +4848,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E191" s="7" t="inlineStr">
+      <c r="E191" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -4841,7 +4857,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4859,7 +4875,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E192" s="5" t="inlineStr">
+      <c r="E192" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -4868,7 +4884,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4886,7 +4902,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -4895,7 +4911,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4913,7 +4929,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E194" s="7" t="inlineStr">
+      <c r="E194" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -4922,7 +4938,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4945,7 +4961,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4968,253 +4984,277 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E198" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32H5E5VK</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32H5E5VK</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32H5F5ZJ</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5237,7 +5277,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32H5F5ZJ</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5248,7 +5288,7 @@
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
@@ -5260,237 +5300,277 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32H5E5VJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D209" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32H5E5VJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32H5E5ZK</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D211" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32H5E5ZK</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32H5F5LJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32H5F5LJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32H5F5IJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32H5F5IJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32H5E5LJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32H5E5LJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32H5E5ZJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5513,7 +5593,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32H5E5ZJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5524,7 +5604,7 @@
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
@@ -5536,189 +5616,838 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32H5F5VJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D221" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32H5F5VJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32H5E5IJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D223" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32H5E5IJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32H5E5IK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E225" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32H5E5IK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32H5E5LK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32H5E5LK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>STM32H5E5VK</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>STM32H5E5VK</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
           <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E228" s="3" t="inlineStr">
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>STM32H5F5ZJ</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>STM32H5F5ZJ</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>STM32H5E5VJ</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>STM32H5E5VJ</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZK</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZK</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>STM32H5F5LJ</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>STM32H5F5LJ</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>STM32H5F5IJ</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>STM32H5F5IJ</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>STM32H5E5LJ</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>STM32H5E5LJ</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZJ</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZJ</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>STM32H5F5VJ</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>STM32H5F5VJ</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>STM32H5E5IJ</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>STM32H5E5IJ</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>STM32H5E5IK</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>STM32H5E5IK</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>STM32H5E5LK</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>STM32H5E5LK</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E228"/>
+  <autoFilter ref="A18:E255"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32H5 series - diff.xlsx
+++ b/product_selector_out/STM32H5 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$282</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5421</v>
+        <v>5412</v>
       </c>
     </row>
     <row r="18">
@@ -3179,18 +3179,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3202,99 +3206,95 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3306,22 +3306,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3333,22 +3333,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3387,22 +3387,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -3414,17 +3414,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -3441,17 +3441,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -3468,17 +3468,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -3495,18 +3495,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3518,180 +3522,176 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3703,22 +3703,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3730,22 +3730,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3757,22 +3757,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3784,22 +3784,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -3811,18 +3811,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3834,148 +3838,152 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -3987,22 +3995,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -4014,22 +4022,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
@@ -4041,54 +4049,46 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4100,22 +4100,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4127,18 +4127,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D163" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -4150,189 +4154,201 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4340,70 +4356,70 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E172" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4413,78 +4429,70 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E174" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4507,7 +4515,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4530,295 +4538,319 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D181" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E186" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E187" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E188" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
@@ -4830,22 +4862,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
@@ -4857,99 +4889,87 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -4961,18 +4981,18 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
@@ -4984,211 +5004,199 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E198" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E199" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E200" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -5200,22 +5208,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -5227,22 +5235,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -5254,477 +5262,485 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E210" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E211" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E212" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E215" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E217" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E218" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E222" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E223" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E224" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5739,19 +5755,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E225" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5766,7 +5782,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -5778,7 +5794,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5793,7 +5809,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
@@ -5805,7 +5821,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5828,7 +5844,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5851,317 +5867,369 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D230" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32H5E5VK</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D232" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32H5E5VK</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32H5F5ZJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32H5F5ZJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STM32H5E5VJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>STM32H5E5VJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>STM32H5E5ZK</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>STM32H5E5ZK</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>STM32H5F5LJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>STM32H5F5LJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>STM32H5F5IJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>STM32H5F5IJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
@@ -6173,18 +6241,18 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STM32H5E5LJ</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
@@ -6196,258 +6264,919 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STM32H5E5LJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>STM32H5E5ZJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D246" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>STM32H5E5ZJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E247" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>STM32H5F5VJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>STM32H5F5VJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>STM32H5E5IJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>STM32H5E5IJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E251" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>STM32H5E5IK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E252" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>STM32H5E5IK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>STM32H5E5LK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E254" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>STM32H5E5LK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>STM32H5E5VK</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>STM32H5E5VK</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
           <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E255" s="3" t="inlineStr">
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>STM32H5F5ZJ</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>STM32H5F5ZJ</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>STM32H5E5VJ</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>STM32H5E5VJ</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZK</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZK</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>STM32H5F5LJ</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>STM32H5F5LJ</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>STM32H5F5IJ</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>STM32H5F5IJ</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>STM32H5E5LJ</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>STM32H5E5LJ</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZJ</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZJ</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>STM32H5F5VJ</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>STM32H5F5VJ</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>STM32H5E5IJ</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>STM32H5E5IJ</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>STM32H5E5IK</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>STM32H5E5IK</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>STM32H5E5LK</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>STM32H5E5LK</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E255"/>
+  <autoFilter ref="A18:E282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32H5 series - diff.xlsx
+++ b/product_selector_out/STM32H5 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$291</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E282"/>
+  <dimension ref="A1:E291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5610</v>
+        <v>5695</v>
       </c>
     </row>
     <row r="6">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5412</v>
+        <v>5488</v>
       </c>
     </row>
     <row r="18">
@@ -3301,27 +3301,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3346,9 +3342,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3361,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3373,9 +3369,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3387,22 +3383,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3414,22 +3410,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -3454,9 +3450,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3469,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3481,9 +3477,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3495,22 +3491,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3535,9 +3531,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3550,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3562,9 +3558,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3576,22 +3572,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3616,9 +3612,9 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3631,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3643,9 +3639,9 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3657,18 +3653,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3680,13 +3680,13 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -3698,54 +3698,46 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3754,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3770,9 +3762,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3784,22 +3776,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3811,22 +3803,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3838,22 +3830,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3862,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3878,9 +3870,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3892,22 +3884,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3919,22 +3911,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3943,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3959,9 +3951,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3973,22 +3965,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -4000,22 +3992,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4024,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4040,9 +4032,9 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4054,18 +4046,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -4077,99 +4073,91 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4181,22 +4169,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E165" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4208,22 +4196,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -4235,22 +4223,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -4262,22 +4250,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -4289,17 +4277,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -4316,17 +4304,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -4343,17 +4331,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -4370,17 +4358,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
@@ -4397,17 +4385,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -4424,17 +4412,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -4451,18 +4439,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4474,59 +4466,67 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -4538,108 +4538,92 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E180" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4651,17 +4635,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -4678,17 +4662,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -4705,17 +4689,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
@@ -4732,22 +4716,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4772,9 +4756,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4770,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4799,9 +4783,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -4813,22 +4797,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E189" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -4840,22 +4824,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E190" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4867,22 +4851,22 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -4894,18 +4878,22 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -4917,71 +4905,83 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5004,7 +5004,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5027,18 +5027,18 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -5050,18 +5050,18 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -5073,135 +5073,115 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E201" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E202" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E203" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E204" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -5213,22 +5193,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E205" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5240,22 +5220,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E206" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -5267,22 +5247,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -5294,22 +5274,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E208" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -5321,22 +5301,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E209" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5348,22 +5328,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -5375,22 +5355,22 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E211" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -5402,22 +5382,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5429,18 +5409,22 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -5452,40 +5436,44 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
@@ -5497,22 +5485,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -5524,22 +5512,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
@@ -5551,81 +5539,69 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E218" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E219" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E220" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -5637,22 +5613,22 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E221" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5664,22 +5640,22 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E222" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -5691,22 +5667,22 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E223" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -5718,22 +5694,22 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E224" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -5745,17 +5721,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -5772,17 +5748,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -5799,17 +5775,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
@@ -5826,18 +5802,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5849,207 +5829,199 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E231" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E232" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E233" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E234" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E235" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E236" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -6061,17 +6033,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -6088,17 +6060,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -6115,17 +6087,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
@@ -6142,22 +6114,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E240" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -6169,22 +6141,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E241" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -6196,22 +6168,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E242" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -6223,18 +6195,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E243" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -6246,234 +6222,226 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E246" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E247" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E248" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E249" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E249" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E250" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E251" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E252" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -6485,22 +6453,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E253" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -6512,22 +6480,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E254" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -6539,18 +6507,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D255" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E255" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -6562,163 +6534,191 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E256" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>STM32H5E5VK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E259" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>STM32H5E5VK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E260" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E260" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>STM32H5F5ZJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E261" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>STM32H5F5ZJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E262" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>STM32H5E5VJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6741,7 +6741,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>STM32H5E5VJ</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6752,7 +6752,7 @@
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
@@ -6764,18 +6764,18 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>STM32H5E5ZK</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
@@ -6787,18 +6787,18 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>STM32H5E5ZK</t>
+          <t>STM32H533ZE</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
@@ -6810,18 +6810,18 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>STM32H5F5LJ</t>
+          <t>STM32H533ZE</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -6833,18 +6833,18 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>STM32H5F5LJ</t>
+          <t>STM32H5E5VK</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
@@ -6856,18 +6856,18 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>STM32H5F5IJ</t>
+          <t>STM32H5E5VK</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
@@ -6879,18 +6879,18 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>STM32H5F5IJ</t>
+          <t>STM32H5F5ZJ</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
@@ -6902,18 +6902,18 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>STM32H5E5LJ</t>
+          <t>STM32H5F5ZJ</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
@@ -6925,18 +6925,18 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>STM32H5E5LJ</t>
+          <t>STM32H5E5VJ</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -6948,18 +6948,18 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>STM32H5E5ZJ</t>
+          <t>STM32H5E5VJ</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -6971,18 +6971,18 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>STM32H5E5ZJ</t>
+          <t>STM32H5E5ZK</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
@@ -6994,18 +6994,18 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>STM32H5F5VJ</t>
+          <t>STM32H5E5ZK</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -7017,18 +7017,18 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>STM32H5F5VJ</t>
+          <t>STM32H5F5LJ</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -7040,18 +7040,18 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>STM32H5E5IJ</t>
+          <t>STM32H5F5LJ</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -7063,18 +7063,18 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>STM32H5E5IJ</t>
+          <t>STM32H5F5IJ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
@@ -7086,18 +7086,18 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>STM32H5E5IK</t>
+          <t>STM32H5F5IJ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
@@ -7109,18 +7109,18 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>STM32H5E5IK</t>
+          <t>STM32H5E5LJ</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-02-26T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
@@ -7132,18 +7132,18 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>STM32H5E5LK</t>
+          <t>STM32H5E5LJ</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -7155,28 +7155,235 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>STM32H5E5LK</t>
+          <t>STM32H5E5ZJ</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>STM32H5E5ZJ</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
           <t>2026-02-26T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E282" s="3" t="inlineStr">
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>STM32H5F5VJ</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>STM32H5F5VJ</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>STM32H5E5IJ</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>STM32H5E5IJ</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>STM32H5E5IK</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>STM32H5E5IK</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>STM32H5E5LK</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>STM32H5E5LK</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-02-26T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E282"/>
+  <autoFilter ref="A18:E291"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>